--- a/95 Файлы/Допуск. М10/Допуск. М10. Интерлифт-Юг.xlsx
+++ b/95 Файлы/Допуск. М10/Допуск. М10. Интерлифт-Юг.xlsx
@@ -185,7 +185,7 @@
     <t>Наладчик</t>
   </si>
   <si>
-    <t>с 1.04.2026 по 30.04.2026</t>
+    <t>с 1.05.2026 по 31.05.2026</t>
   </si>
 </sst>
 </file>
@@ -493,12 +493,81 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
@@ -510,75 +579,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -877,120 +877,120 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:9" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="B1" s="31" t="s">
+      <c r="B1" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="33"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="45"/>
+      <c r="I1" s="46"/>
     </row>
     <row r="2" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B2" s="34" t="s">
+      <c r="B2" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="35"/>
+      <c r="C2" s="33"/>
       <c r="D2" s="21"/>
-      <c r="E2" s="36" t="s">
+      <c r="E2" s="47" t="s">
         <v>33</v>
       </c>
-      <c r="F2" s="36"/>
-      <c r="G2" s="36"/>
-      <c r="H2" s="36"/>
-      <c r="I2" s="37"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="47"/>
+      <c r="I2" s="48"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B3" s="38" t="s">
+      <c r="B3" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="39"/>
+      <c r="C3" s="26"/>
       <c r="D3" s="10"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="40"/>
-      <c r="G3" s="40"/>
-      <c r="H3" s="40"/>
-      <c r="I3" s="41"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="28"/>
+      <c r="H3" s="28"/>
+      <c r="I3" s="29"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B4" s="38" t="s">
+      <c r="B4" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="39"/>
+      <c r="C4" s="26"/>
       <c r="D4" s="11"/>
-      <c r="E4" s="49" t="s">
+      <c r="E4" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="F4" s="40"/>
-      <c r="G4" s="40"/>
-      <c r="H4" s="40"/>
-      <c r="I4" s="41"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="28"/>
+      <c r="H4" s="28"/>
+      <c r="I4" s="29"/>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B5" s="38" t="s">
+      <c r="B5" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="39"/>
+      <c r="C5" s="26"/>
       <c r="D5" s="12"/>
-      <c r="E5" s="50" t="s">
+      <c r="E5" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="F5" s="50"/>
-      <c r="G5" s="50"/>
-      <c r="H5" s="50"/>
-      <c r="I5" s="51"/>
+      <c r="F5" s="30"/>
+      <c r="G5" s="30"/>
+      <c r="H5" s="30"/>
+      <c r="I5" s="31"/>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B6" s="34" t="s">
+      <c r="B6" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="35"/>
+      <c r="C6" s="33"/>
       <c r="D6" s="22"/>
-      <c r="E6" s="52" t="s">
+      <c r="E6" s="34" t="s">
         <v>32</v>
       </c>
-      <c r="F6" s="52"/>
-      <c r="G6" s="52"/>
-      <c r="H6" s="52"/>
-      <c r="I6" s="53"/>
+      <c r="F6" s="34"/>
+      <c r="G6" s="34"/>
+      <c r="H6" s="34"/>
+      <c r="I6" s="35"/>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B7" s="38" t="s">
+      <c r="B7" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="39"/>
+      <c r="C7" s="26"/>
       <c r="D7" s="11"/>
-      <c r="E7" s="42"/>
-      <c r="F7" s="42"/>
-      <c r="G7" s="42"/>
-      <c r="H7" s="42"/>
-      <c r="I7" s="43"/>
+      <c r="E7" s="36"/>
+      <c r="F7" s="36"/>
+      <c r="G7" s="36"/>
+      <c r="H7" s="36"/>
+      <c r="I7" s="37"/>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B8" s="13"/>
       <c r="C8" s="11"/>
       <c r="D8" s="11"/>
-      <c r="E8" s="26" t="s">
+      <c r="E8" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="F8" s="26"/>
-      <c r="G8" s="26"/>
-      <c r="H8" s="26"/>
-      <c r="I8" s="44"/>
+      <c r="F8" s="38"/>
+      <c r="G8" s="38"/>
+      <c r="H8" s="38"/>
+      <c r="I8" s="39"/>
     </row>
     <row r="9" spans="2:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="45" t="s">
+      <c r="B9" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="46"/>
-      <c r="D9" s="46"/>
-      <c r="E9" s="46"/>
-      <c r="F9" s="46"/>
-      <c r="G9" s="46"/>
-      <c r="H9" s="46"/>
-      <c r="I9" s="47"/>
+      <c r="C9" s="41"/>
+      <c r="D9" s="41"/>
+      <c r="E9" s="41"/>
+      <c r="F9" s="41"/>
+      <c r="G9" s="41"/>
+      <c r="H9" s="41"/>
+      <c r="I9" s="42"/>
     </row>
     <row r="10" spans="2:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="8" t="s">
@@ -999,10 +999,10 @@
       <c r="C10" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="48" t="s">
+      <c r="D10" s="43" t="s">
         <v>9</v>
       </c>
-      <c r="E10" s="48"/>
+      <c r="E10" s="43"/>
       <c r="F10" s="7" t="s">
         <v>14</v>
       </c>
@@ -1113,49 +1113,49 @@
       </c>
     </row>
     <row r="15" spans="2:9" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="27" t="s">
+      <c r="B15" s="50" t="s">
         <v>10</v>
       </c>
-      <c r="C15" s="28"/>
-      <c r="D15" s="28"/>
-      <c r="E15" s="28"/>
-      <c r="F15" s="28"/>
-      <c r="G15" s="28"/>
-      <c r="H15" s="28"/>
-      <c r="I15" s="28"/>
+      <c r="C15" s="51"/>
+      <c r="D15" s="51"/>
+      <c r="E15" s="51"/>
+      <c r="F15" s="51"/>
+      <c r="G15" s="51"/>
+      <c r="H15" s="51"/>
+      <c r="I15" s="51"/>
     </row>
     <row r="16" spans="2:9" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="30" t="s">
+      <c r="B16" s="53" t="s">
         <v>29</v>
       </c>
-      <c r="C16" s="30"/>
-      <c r="D16" s="30"/>
-      <c r="E16" s="30"/>
-      <c r="F16" s="30"/>
+      <c r="C16" s="53"/>
+      <c r="D16" s="53"/>
+      <c r="E16" s="53"/>
+      <c r="F16" s="53"/>
       <c r="G16" s="5"/>
-      <c r="H16" s="29" t="s">
+      <c r="H16" s="52" t="s">
         <v>30</v>
       </c>
-      <c r="I16" s="29"/>
+      <c r="I16" s="52"/>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B17" s="25" t="s">
+      <c r="B17" s="49" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="25"/>
-      <c r="D17" s="25"/>
-      <c r="E17" s="25"/>
+      <c r="C17" s="49"/>
+      <c r="D17" s="49"/>
+      <c r="E17" s="49"/>
       <c r="F17" s="6"/>
       <c r="G17" s="6"/>
-      <c r="H17" s="26" t="s">
+      <c r="H17" s="38" t="s">
         <v>12</v>
       </c>
-      <c r="I17" s="26"/>
+      <c r="I17" s="38"/>
     </row>
     <row r="18" spans="2:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="3">
         <f ca="1">TODAY()</f>
-        <v>46112</v>
+        <v>46140</v>
       </c>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.25">
@@ -1165,27 +1165,27 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="B17:E17"/>
+    <mergeCell ref="H17:I17"/>
+    <mergeCell ref="B15:I15"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="B1:I1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="E2:I2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="E3:I3"/>
+    <mergeCell ref="E7:I7"/>
+    <mergeCell ref="E8:I8"/>
+    <mergeCell ref="B9:I9"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="B7:C7"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="E4:I4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="E5:I5"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="E6:I6"/>
-    <mergeCell ref="E7:I7"/>
-    <mergeCell ref="E8:I8"/>
-    <mergeCell ref="B9:I9"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B1:I1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="E2:I2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="E3:I3"/>
-    <mergeCell ref="B17:E17"/>
-    <mergeCell ref="H17:I17"/>
-    <mergeCell ref="B15:I15"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="B16:F16"/>
   </mergeCells>
   <pageMargins left="0.31388888888888899" right="0.31388888888888899" top="0.55000000000000004" bottom="0.55000000000000004" header="0.31388888888888899" footer="0.31388888888888899"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="portrait" r:id="rId1"/>
